--- a/artfynd/A 55576-2025 artfynd.xlsx
+++ b/artfynd/A 55576-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131639495</v>
+        <v>130856922</v>
       </c>
       <c r="B2" t="n">
-        <v>57136</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pulshöjd, Pulshöjd, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470160</v>
+        <v>470237</v>
       </c>
       <c r="R2" t="n">
-        <v>6599691</v>
+        <v>6599727</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131639550</v>
+        <v>131639495</v>
       </c>
       <c r="B3" t="n">
-        <v>57136</v>
+        <v>57162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -855,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470119</v>
+        <v>470160</v>
       </c>
       <c r="R3" t="n">
-        <v>6599735</v>
+        <v>6599691</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,6 +905,253 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131639550</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pulshöjd, Pulshöjd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>470119</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6599735</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kroppa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131639523</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57165</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pulshöjd, Pulshöjd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>470081</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6599724</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kroppa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
